--- a/preschool-teaching/output/09 4 Senarai Bukti Proses Kerja + Lampiran 4 Perakuan Pembimbing/4 Senarai Bukti Proses Kerja (P851).xlsx
+++ b/preschool-teaching/output/09 4 Senarai Bukti Proses Kerja + Lampiran 4 Perakuan Pembimbing/4 Senarai Bukti Proses Kerja (P851).xlsx
@@ -1313,16 +1313,8 @@
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>P02</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>Proses Kerja 2</t>
-        </is>
-      </c>
+      <c r="A6" s="19" t="n"/>
+      <c r="B6" s="20" t="n"/>
       <c r="C6" s="23" t="n">
         <v>4</v>
       </c>
@@ -1363,16 +1355,8 @@
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>Proses Kerja 3</t>
-        </is>
-      </c>
+      <c r="A8" s="19" t="n"/>
+      <c r="B8" s="20" t="n"/>
       <c r="C8" s="19" t="n">
         <v>6</v>
       </c>
@@ -1430,16 +1414,8 @@
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>Proses Kerja 4</t>
-        </is>
-      </c>
+      <c r="A11" s="19" t="n"/>
+      <c r="B11" s="20" t="n"/>
       <c r="C11" s="23" t="n">
         <v>9</v>
       </c>
